--- a/Data/Tables/StatusDefine.xlsx
+++ b/Data/Tables/StatusDefine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="18052" windowHeight="8655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
   <si>
     <t>状态名称（可以没有）</t>
   </si>
@@ -40,6 +40,9 @@
     <t>状态数值</t>
   </si>
   <si>
+    <t>目标</t>
+  </si>
+  <si>
     <t>持续时间</t>
   </si>
   <si>
@@ -67,7 +70,94 @@
     <t>Value</t>
   </si>
   <si>
+    <t>Target</t>
+  </si>
+  <si>
     <t>Duration</t>
+  </si>
+  <si>
+    <t>群居（群狼）</t>
+  </si>
+  <si>
+    <t>速度变化</t>
+  </si>
+  <si>
+    <t>自我保护（穿山甲）</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>禁锢（穿山甲）</t>
+  </si>
+  <si>
+    <t>显形（孤魂）</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>限制法力（魃）</t>
+  </si>
+  <si>
+    <t>修为减少</t>
+  </si>
+  <si>
+    <t>吸取法力1（魃）</t>
+  </si>
+  <si>
+    <t>吸取法力2（魃）</t>
+  </si>
+  <si>
+    <t>伤害变化</t>
+  </si>
+  <si>
+    <t>红色形态（厚甲蟹）</t>
+  </si>
+  <si>
+    <t>物理减伤</t>
+  </si>
+  <si>
+    <t>蓝色形态（厚甲蟹）</t>
+  </si>
+  <si>
+    <t>法术减伤</t>
+  </si>
+  <si>
+    <t>绿色形态（厚甲蟹）</t>
+  </si>
+  <si>
+    <t>武器减伤</t>
+  </si>
+  <si>
+    <t>向下水流（化蛇）</t>
+  </si>
+  <si>
+    <t>额外向下速度</t>
+  </si>
+  <si>
+    <t>向左水流（化蛇）</t>
+  </si>
+  <si>
+    <t>额外向左速度</t>
+  </si>
+  <si>
+    <t>向右水流（化蛇）</t>
+  </si>
+  <si>
+    <t>额外向右速度</t>
+  </si>
+  <si>
+    <t>向上水流（化蛇）</t>
+  </si>
+  <si>
+    <t>额外向上速度</t>
+  </si>
+  <si>
+    <t>寻血（猎犬）</t>
+  </si>
+  <si>
+    <t>减速（陷阱）</t>
   </si>
 </sst>
 </file>
@@ -707,7 +797,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -724,6 +814,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -878,15 +971,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A3:F72" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F72" etc:filterBottomFollowUsedRange="0"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A3:G72" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G72" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="7">
     <tableColumn id="1" name="Key"/>
     <tableColumn id="2" name="ID"/>
     <tableColumn id="3" name="Name"/>
     <tableColumn id="4" name="Type"/>
     <tableColumn id="5" name="Value" dataDxfId="0"/>
-    <tableColumn id="6" name="Duration"/>
+    <tableColumn id="6" name="Target"/>
+    <tableColumn id="7" name="Duration"/>
   </tableColumns>
   <tableStyleInfo name="TableStylePreset3_Accent1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1142,16 +1236,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F72"/>
-  <sheetFormatPr defaultColWidth="14.2916666666667" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <dimension ref="A1:G72"/>
+  <sheetFormatPr defaultColWidth="14.2920353982301" defaultRowHeight="12.35" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="8.25833333333333" style="3" customWidth="1"/>
-    <col min="2" max="2" width="7.29166666666667" style="3" customWidth="1"/>
-    <col min="3" max="3" width="38.75" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="14.2916666666667" style="1"/>
+    <col min="1" max="1" width="8.25663716814159" style="3" customWidth="1"/>
+    <col min="2" max="2" width="7.29203539823009" style="3" customWidth="1"/>
+    <col min="3" max="3" width="38.7522123893805" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="14.2920353982301" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="3:6">
+    <row r="1" s="1" customFormat="1" ht="12.4" spans="3:7">
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1164,206 +1258,423 @@
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:5">
+        <v>13</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="12.4" spans="1:7">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:5">
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="12.4" spans="1:7">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:5">
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2">
+        <v>200</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="12.4" spans="1:7">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="2">
         <v>3</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:5">
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="6">
+        <v>-10</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="12.4" spans="1:7">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="2">
         <v>4</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:5">
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-100</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:5">
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A9" s="2">
         <v>6</v>
       </c>
       <c r="B9" s="2">
         <v>6</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:5">
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A10" s="2">
         <v>7</v>
       </c>
       <c r="B10" s="2">
         <v>7</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:5">
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A11" s="2">
         <v>8</v>
       </c>
       <c r="B11" s="2">
         <v>8</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:5">
+      <c r="C11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="1">
+        <v>90</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A12" s="2">
         <v>9</v>
       </c>
       <c r="B12" s="2">
         <v>9</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:5">
+      <c r="C12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="1">
+        <v>90</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A13" s="2">
         <v>10</v>
       </c>
       <c r="B13" s="2">
         <v>10</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:5">
+      <c r="C13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="1">
+        <v>90</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A14" s="2">
         <v>11</v>
       </c>
       <c r="B14" s="2">
         <v>11</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:5">
+      <c r="C14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A15" s="1">
         <v>12</v>
       </c>
       <c r="B15" s="3">
         <v>12</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:5">
+      <c r="C15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A16" s="2">
         <v>13</v>
       </c>
       <c r="B16" s="2">
         <v>13</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:5">
+      <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A17" s="2">
         <v>14</v>
       </c>
       <c r="B17" s="2">
         <v>14</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:5">
+      <c r="C17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A18" s="2">
         <v>15</v>
       </c>
       <c r="B18" s="2">
         <v>15</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:5">
+      <c r="C18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="12.4" spans="1:7">
       <c r="A19" s="2">
         <v>16</v>
       </c>
       <c r="B19" s="2">
         <v>16</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:5">
+      <c r="C19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1">
+        <v>-0.5</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:7">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -1371,9 +1682,9 @@
         <v>17</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="E20" s="5"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:5">
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:7">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -1381,9 +1692,9 @@
         <v>18</v>
       </c>
       <c r="C21" s="2"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:5">
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:7">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -1391,9 +1702,9 @@
         <v>19</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:5">
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:7">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -1401,9 +1712,9 @@
         <v>20</v>
       </c>
       <c r="C23" s="2"/>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:5">
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:7">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -1412,8 +1723,9 @@
       </c>
       <c r="C24" s="2"/>
       <c r="E24" s="5"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:5">
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:7">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -1422,8 +1734,9 @@
       </c>
       <c r="C25" s="2"/>
       <c r="E25" s="5"/>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:5">
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:7">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -1432,8 +1745,9 @@
       </c>
       <c r="C26" s="2"/>
       <c r="E26" s="5"/>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:5">
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:7">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -1442,8 +1756,9 @@
       </c>
       <c r="C27" s="2"/>
       <c r="E27" s="5"/>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:5">
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:7">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -1452,8 +1767,9 @@
       </c>
       <c r="C28" s="2"/>
       <c r="E28" s="5"/>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:5">
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:7">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -1462,8 +1778,9 @@
       </c>
       <c r="C29" s="2"/>
       <c r="E29" s="5"/>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:5">
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:7">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -1472,8 +1789,9 @@
       </c>
       <c r="C30" s="2"/>
       <c r="E30" s="5"/>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:5">
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:7">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -1482,8 +1800,9 @@
       </c>
       <c r="C31" s="2"/>
       <c r="E31" s="5"/>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:5">
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:7">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -1492,6 +1811,7 @@
       </c>
       <c r="C32" s="2"/>
       <c r="E32" s="5"/>
+      <c r="G32" s="2"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:5">
       <c r="A33" s="2">
